--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131242903</v>
+        <v>131242966</v>
       </c>
       <c r="B2" t="n">
         <v>57881</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325571</v>
+        <v>325580</v>
       </c>
       <c r="R2" t="n">
-        <v>6445484</v>
+        <v>6445675</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131242966</v>
+        <v>131242903</v>
       </c>
       <c r="B3" t="n">
         <v>57881</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325580</v>
+        <v>325571</v>
       </c>
       <c r="R3" t="n">
-        <v>6445675</v>
+        <v>6445484</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131242966</v>
+        <v>131242903</v>
       </c>
       <c r="B2" t="n">
         <v>57881</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325580</v>
+        <v>325571</v>
       </c>
       <c r="R2" t="n">
-        <v>6445675</v>
+        <v>6445484</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131242903</v>
+        <v>131242966</v>
       </c>
       <c r="B3" t="n">
         <v>57881</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325571</v>
+        <v>325580</v>
       </c>
       <c r="R3" t="n">
-        <v>6445484</v>
+        <v>6445675</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131242966</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131242903</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131242916</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131243009</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131242990</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>131242936</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>131242953</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131242966</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131242903</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131242916</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131243009</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131242990</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>131242936</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>131242953</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131242966</v>
+        <v>131242903</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325580</v>
+        <v>325571</v>
       </c>
       <c r="R2" t="n">
-        <v>6445675</v>
+        <v>6445484</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131242903</v>
+        <v>131242966</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325571</v>
+        <v>325580</v>
       </c>
       <c r="R3" t="n">
-        <v>6445484</v>
+        <v>6445675</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131242903</v>
+        <v>131242966</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325571</v>
+        <v>325580</v>
       </c>
       <c r="R2" t="n">
-        <v>6445484</v>
+        <v>6445675</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131242966</v>
+        <v>131242903</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325580</v>
+        <v>325571</v>
       </c>
       <c r="R3" t="n">
-        <v>6445675</v>
+        <v>6445484</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131242966</v>
+        <v>131242903</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325580</v>
+        <v>325571</v>
       </c>
       <c r="R2" t="n">
-        <v>6445675</v>
+        <v>6445484</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131242903</v>
+        <v>131242966</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325571</v>
+        <v>325580</v>
       </c>
       <c r="R3" t="n">
-        <v>6445484</v>
+        <v>6445675</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,7 +888,7 @@
         <v>131242916</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131243009</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131242990</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>131242936</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>131242953</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131242903</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131242966</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131242916</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131243009</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131242990</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>131242936</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>131242953</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131242903</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131242966</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131242916</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131243009</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131242990</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>131242936</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>131242953</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131242903</v>
+        <v>131242872</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325571</v>
+        <v>325636</v>
       </c>
       <c r="R2" t="n">
-        <v>6445484</v>
+        <v>6445432</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -780,14 +780,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131242966</v>
+        <v>131242903</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325580</v>
+        <v>325571</v>
       </c>
       <c r="R3" t="n">
-        <v>6445675</v>
+        <v>6445484</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,11 +888,11 @@
         <v>131242916</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -990,14 +990,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131243009</v>
+        <v>131242936</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1023,7 +1023,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325560</v>
+        <v>325557</v>
       </c>
       <c r="R5" t="n">
-        <v>6445682</v>
+        <v>6445633</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,14 +1095,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131242990</v>
+        <v>131242953</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325558</v>
+        <v>325566</v>
       </c>
       <c r="R6" t="n">
-        <v>6445683</v>
+        <v>6445648</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,14 +1200,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131242936</v>
+        <v>131242966</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1233,7 +1233,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325557</v>
+        <v>325580</v>
       </c>
       <c r="R7" t="n">
-        <v>6445633</v>
+        <v>6445675</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,14 +1305,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131242953</v>
+        <v>131242990</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325566</v>
+        <v>325558</v>
       </c>
       <c r="R8" t="n">
-        <v>6445648</v>
+        <v>6445683</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1407,6 +1407,213 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131243009</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Medjolingen, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>325560</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6445682</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131242893</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Medjolingen, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>325615</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6445440</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5866-2026 artfynd.xlsx
+++ b/artfynd/A 5866-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242872</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242903</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242916</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242936</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242953</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242966</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242990</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131243009</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,8 +1659,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242893</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>